--- a/artfynd/A 26727-2025 artfynd.xlsx
+++ b/artfynd/A 26727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153246</v>
       </c>
       <c r="B2" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26727-2025 artfynd.xlsx
+++ b/artfynd/A 26727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153246</v>
       </c>
       <c r="B2" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26727-2025 artfynd.xlsx
+++ b/artfynd/A 26727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153246</v>
       </c>
       <c r="B2" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26727-2025 artfynd.xlsx
+++ b/artfynd/A 26727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153246</v>
       </c>
       <c r="B2" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26727-2025 artfynd.xlsx
+++ b/artfynd/A 26727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153246</v>
       </c>
       <c r="B2" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26727-2025 artfynd.xlsx
+++ b/artfynd/A 26727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130153246</v>
       </c>
       <c r="B2" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
